--- a/docs/Login-Instruktur-PIK.xlsx
+++ b/docs/Login-Instruktur-PIK.xlsx
@@ -559,7 +559,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -618,7 +617,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>lailyGGPIK</t>
+          <t>lailysor</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -658,7 +657,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>oliviaGGPIK</t>
+          <t>oliviana</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -698,7 +697,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>stefannyPIK2</t>
+          <t>stefanny</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -738,7 +737,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>susanPIK</t>
+          <t>susanwid</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -778,7 +777,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>violettaPIK</t>
+          <t>violetta</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
